--- a/output/laminas_comunales/comunal_s_isapre_a_2024_la_araucania.xlsx
+++ b/output/laminas_comunales/comunal_s_isapre_a_2024_la_araucania.xlsx
@@ -384,82 +384,82 @@
         </is>
       </c>
       <c r="C2">
-        <v>36709</v>
+        <v>12.25377453909398</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>9115</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Villarrica</t>
+          <t>Pucón</t>
         </is>
       </c>
       <c r="C3">
-        <v>4591</v>
+        <v>7.269485481406011</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9201</t>
+          <t>9120</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Angol</t>
+          <t>Villarrica</t>
         </is>
       </c>
       <c r="C4">
-        <v>3086</v>
+        <v>5.920891422380995</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>9115</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pucón</t>
+          <t>Angol</t>
         </is>
       </c>
       <c r="C5">
-        <v>2854</v>
+        <v>5.22917902228247</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9112</t>
+          <t>9211</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Padre Las Casas</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="C6">
-        <v>2390</v>
+        <v>4.407226691283133</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>9211</t>
+          <t>9203</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Curacautín</t>
         </is>
       </c>
       <c r="C7">
-        <v>1671</v>
+        <v>3.414238710600353</v>
       </c>
     </row>
     <row r="8">
@@ -474,337 +474,337 @@
         </is>
       </c>
       <c r="C8">
-        <v>1481</v>
+        <v>3.265135147052339</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>9119</t>
+          <t>9210</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Vilcún</t>
+          <t>Traiguén</t>
         </is>
       </c>
       <c r="C9">
-        <v>1043</v>
+        <v>3.263083116268056</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9114</t>
+          <t>9209</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pitrufquén</t>
+          <t>Renaico</t>
         </is>
       </c>
       <c r="C10">
-        <v>888</v>
+        <v>3.179575534497611</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>9111</t>
+          <t>9119</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nueva Imperial</t>
+          <t>Vilcún</t>
         </is>
       </c>
       <c r="C11">
-        <v>770</v>
+        <v>3.047479912344777</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>9105</t>
+          <t>9114</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Freire</t>
+          <t>Pitrufquén</t>
         </is>
       </c>
       <c r="C12">
-        <v>766</v>
+        <v>2.95970402959704</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>9203</t>
+          <t>9112</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Curacautín</t>
+          <t>Padre Las Casas</t>
         </is>
       </c>
       <c r="C13">
-        <v>716</v>
+        <v>2.822290188113317</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>9202</t>
+          <t>9105</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Collipulli</t>
+          <t>Freire</t>
         </is>
       </c>
       <c r="C14">
-        <v>708</v>
+        <v>2.68621124982466</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>9109</t>
+          <t>9107</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Loncoche</t>
+          <t>Gorbea</t>
         </is>
       </c>
       <c r="C15">
-        <v>706</v>
+        <v>2.618039726473461</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>9210</t>
+          <t>9208</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Traiguén</t>
+          <t>Purén</t>
         </is>
       </c>
       <c r="C16">
-        <v>689</v>
+        <v>2.591777320173259</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>9102</t>
+          <t>9109</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Carahue</t>
+          <t>Loncoche</t>
         </is>
       </c>
       <c r="C17">
-        <v>488</v>
+        <v>2.552514552225316</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>9103</t>
+          <t>9202</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cunco</t>
+          <t>Collipulli</t>
         </is>
       </c>
       <c r="C18">
-        <v>425</v>
+        <v>2.498676548438327</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>9209</t>
+          <t>9110</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Renaico</t>
+          <t>Melipeuco</t>
         </is>
       </c>
       <c r="C19">
-        <v>406</v>
+        <v>2.372284204345273</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>9107</t>
+          <t>9118</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Gorbea</t>
+          <t>Toltén</t>
         </is>
       </c>
       <c r="C20">
-        <v>402</v>
+        <v>2.268413917758699</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>9208</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Purén</t>
+          <t>Perquenco</t>
         </is>
       </c>
       <c r="C21">
-        <v>365</v>
+        <v>2.218366588176973</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>9117</t>
+          <t>9205</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Teodoro Schmidt</t>
+          <t>Lonquimay</t>
         </is>
       </c>
       <c r="C22">
-        <v>305</v>
+        <v>2.203989703989704</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>9205</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lonquimay</t>
+          <t>Nueva Imperial</t>
         </is>
       </c>
       <c r="C23">
-        <v>274</v>
+        <v>2.076479154306672</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>9118</t>
+          <t>9103</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Toltén</t>
+          <t>Cunco</t>
         </is>
       </c>
       <c r="C24">
-        <v>251</v>
+        <v>2.032423126584094</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>9121</t>
+          <t>9207</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cholchol</t>
+          <t>Lumaco</t>
         </is>
       </c>
       <c r="C25">
-        <v>232</v>
+        <v>1.88737306390399</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>9106</t>
+          <t>9102</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Galvarino</t>
+          <t>Carahue</t>
         </is>
       </c>
       <c r="C26">
-        <v>217</v>
+        <v>1.79233848753076</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>9117</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Melipeuco</t>
+          <t>Teodoro Schmidt</t>
         </is>
       </c>
       <c r="C27">
-        <v>202</v>
+        <v>1.709737092886373</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9116</t>
+          <t>9121</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Cholchol</t>
         </is>
       </c>
       <c r="C28">
-        <v>193</v>
+        <v>1.582969432314411</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>9207</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Lumaco</t>
+          <t>Los Sauces</t>
         </is>
       </c>
       <c r="C29">
-        <v>184</v>
+        <v>1.499039077514414</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>9106</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Perquenco</t>
+          <t>Galvarino</t>
         </is>
       </c>
       <c r="C30">
-        <v>179</v>
+        <v>1.438515081206497</v>
       </c>
     </row>
     <row r="31">
@@ -819,22 +819,22 @@
         </is>
       </c>
       <c r="C31">
-        <v>131</v>
+        <v>1.382439848037146</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>9206</t>
+          <t>9116</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Los Sauces</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="C32">
-        <v>117</v>
+        <v>1.346824842986741</v>
       </c>
     </row>
     <row r="33">
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="C33">
-        <v>65</v>
+        <v>0.7120166502355132</v>
       </c>
     </row>
   </sheetData>
@@ -905,7 +905,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a ISAPRE</t>
+          <t>Porcentaje de residentes afiliados a ISAPRE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
